--- a/usd_krw_1m.xlsx
+++ b/usd_krw_1m.xlsx
@@ -25,9 +25,6 @@
     <t>02:00 종가</t>
   </si>
   <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
     <t>2026-04-21</t>
   </si>
   <si>
@@ -86,6 +83,9 @@
   </si>
   <si>
     <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
   </si>
 </sst>
 </file>
@@ -263,67 +263,67 @@
               <c:strCache>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>2026-04-20</c:v>
+                  <c:v>2026-04-21</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2026-04-21</c:v>
+                  <c:v>2026-04-22</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2026-04-22</c:v>
+                  <c:v>2026-04-23</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2026-04-23</c:v>
+                  <c:v>2026-04-24</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2026-04-24</c:v>
+                  <c:v>2026-04-27</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2026-04-27</c:v>
+                  <c:v>2026-04-28</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2026-04-28</c:v>
+                  <c:v>2026-04-29</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2026-04-29</c:v>
+                  <c:v>2026-04-30</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2026-04-30</c:v>
+                  <c:v>2026-05-04</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2026-05-04</c:v>
+                  <c:v>2026-05-06</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2026-05-06</c:v>
+                  <c:v>2026-05-07</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2026-05-07</c:v>
+                  <c:v>2026-05-08</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2026-05-08</c:v>
+                  <c:v>2026-05-11</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2026-05-11</c:v>
+                  <c:v>2026-05-12</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2026-05-12</c:v>
+                  <c:v>2026-05-13</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2026-05-13</c:v>
+                  <c:v>2026-05-14</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2026-05-14</c:v>
+                  <c:v>2026-05-15</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2026-05-15</c:v>
+                  <c:v>2026-05-18</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2026-05-18</c:v>
+                  <c:v>2026-05-19</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2026-05-19</c:v>
+                  <c:v>2026-05-20</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2026-05-20</c:v>
+                  <c:v>2026-05-21</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -335,67 +335,67 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>1477.2</c:v>
+                  <c:v>1468.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1468.5</c:v>
+                  <c:v>1476</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1476</c:v>
+                  <c:v>1481</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1481</c:v>
+                  <c:v>1484.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1484.5</c:v>
+                  <c:v>1472.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1472.5</c:v>
+                  <c:v>1473.6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1473.6</c:v>
+                  <c:v>1479</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1479</c:v>
+                  <c:v>1483.3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1483.3</c:v>
+                  <c:v>1462.8</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1462.8</c:v>
+                  <c:v>1455.1</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1455.1</c:v>
+                  <c:v>1454</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1454</c:v>
+                  <c:v>1471.7</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1471.7</c:v>
+                  <c:v>1472.4</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1472.4</c:v>
+                  <c:v>1489.9</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1489.9</c:v>
+                  <c:v>1490.6</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1490.6</c:v>
+                  <c:v>1491</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1491</c:v>
+                  <c:v>1500.8</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1500.8</c:v>
+                  <c:v>1500.3</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1500.3</c:v>
+                  <c:v>1507.8</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1507.8</c:v>
+                  <c:v>1506.8</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1506.8</c:v>
+                  <c:v>1506.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -540,67 +540,67 @@
               <c:strCache>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>2026-04-20</c:v>
+                  <c:v>2026-04-21</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2026-04-21</c:v>
+                  <c:v>2026-04-22</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2026-04-22</c:v>
+                  <c:v>2026-04-23</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2026-04-23</c:v>
+                  <c:v>2026-04-24</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2026-04-24</c:v>
+                  <c:v>2026-04-27</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2026-04-27</c:v>
+                  <c:v>2026-04-28</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2026-04-28</c:v>
+                  <c:v>2026-04-29</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2026-04-29</c:v>
+                  <c:v>2026-04-30</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2026-04-30</c:v>
+                  <c:v>2026-05-04</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2026-05-04</c:v>
+                  <c:v>2026-05-06</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2026-05-06</c:v>
+                  <c:v>2026-05-07</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2026-05-07</c:v>
+                  <c:v>2026-05-08</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2026-05-08</c:v>
+                  <c:v>2026-05-11</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2026-05-11</c:v>
+                  <c:v>2026-05-12</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2026-05-12</c:v>
+                  <c:v>2026-05-13</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2026-05-13</c:v>
+                  <c:v>2026-05-14</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2026-05-14</c:v>
+                  <c:v>2026-05-15</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2026-05-15</c:v>
+                  <c:v>2026-05-18</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2026-05-18</c:v>
+                  <c:v>2026-05-19</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2026-05-19</c:v>
+                  <c:v>2026-05-20</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2026-05-20</c:v>
+                  <c:v>2026-05-21</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -612,67 +612,67 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>1472.8</c:v>
+                  <c:v>1480.8</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1480.8</c:v>
+                  <c:v>1480.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1480.3</c:v>
+                  <c:v>1479.2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1479.2</c:v>
+                  <c:v>1476.8</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1476.8</c:v>
+                  <c:v>1473.6</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1473.6</c:v>
+                  <c:v>1473.2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1473.2</c:v>
+                  <c:v>1488.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1488.5</c:v>
+                  <c:v>1477.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1477.5</c:v>
+                  <c:v>1478.4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1478.4</c:v>
+                  <c:v>1449.4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1449.4</c:v>
+                  <c:v>1456</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1456</c:v>
+                  <c:v>1462.3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1462.3</c:v>
+                  <c:v>1472.7</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1472.7</c:v>
+                  <c:v>1490.9</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1490.9</c:v>
+                  <c:v>1489.3</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1489.3</c:v>
+                  <c:v>1493.4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1493.4</c:v>
+                  <c:v>1497.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1497.5</c:v>
+                  <c:v>1492.9</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1492.9</c:v>
+                  <c:v>1508.7</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1508.7</c:v>
+                  <c:v>1496.7</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1508.7</c:v>
+                  <c:v>1496.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1131,10 +1131,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="3">
-        <v>1477.2</v>
+        <v>1468.5</v>
       </c>
       <c r="C2" s="3">
-        <v>1472.8</v>
+        <v>1480.8</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1142,10 +1142,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>1468.5</v>
+        <v>1476</v>
       </c>
       <c r="C3" s="3">
-        <v>1480.8</v>
+        <v>1480.3</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1153,10 +1153,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="3">
-        <v>1476</v>
+        <v>1481</v>
       </c>
       <c r="C4" s="3">
-        <v>1480.3</v>
+        <v>1479.2</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1164,10 +1164,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="3">
-        <v>1481</v>
+        <v>1484.5</v>
       </c>
       <c r="C5" s="3">
-        <v>1479.2</v>
+        <v>1476.8</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1175,10 +1175,10 @@
         <v>7</v>
       </c>
       <c r="B6" s="3">
-        <v>1484.5</v>
+        <v>1472.5</v>
       </c>
       <c r="C6" s="3">
-        <v>1476.8</v>
+        <v>1473.6</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1186,10 +1186,10 @@
         <v>8</v>
       </c>
       <c r="B7" s="3">
-        <v>1472.5</v>
+        <v>1473.6</v>
       </c>
       <c r="C7" s="3">
-        <v>1473.6</v>
+        <v>1473.2</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1197,10 +1197,10 @@
         <v>9</v>
       </c>
       <c r="B8" s="3">
-        <v>1473.6</v>
+        <v>1479</v>
       </c>
       <c r="C8" s="3">
-        <v>1473.2</v>
+        <v>1488.5</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1208,10 +1208,10 @@
         <v>10</v>
       </c>
       <c r="B9" s="3">
-        <v>1479</v>
+        <v>1483.3</v>
       </c>
       <c r="C9" s="3">
-        <v>1488.5</v>
+        <v>1477.5</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1219,10 +1219,10 @@
         <v>11</v>
       </c>
       <c r="B10" s="3">
-        <v>1483.3</v>
+        <v>1462.8</v>
       </c>
       <c r="C10" s="3">
-        <v>1477.5</v>
+        <v>1478.4</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1230,10 +1230,10 @@
         <v>12</v>
       </c>
       <c r="B11" s="3">
-        <v>1462.8</v>
+        <v>1455.1</v>
       </c>
       <c r="C11" s="3">
-        <v>1478.4</v>
+        <v>1449.4</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1241,10 +1241,10 @@
         <v>13</v>
       </c>
       <c r="B12" s="3">
-        <v>1455.1</v>
+        <v>1454</v>
       </c>
       <c r="C12" s="3">
-        <v>1449.4</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1252,10 +1252,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="3">
-        <v>1454</v>
+        <v>1471.7</v>
       </c>
       <c r="C13" s="3">
-        <v>1456</v>
+        <v>1462.3</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1263,10 +1263,10 @@
         <v>15</v>
       </c>
       <c r="B14" s="3">
-        <v>1471.7</v>
+        <v>1472.4</v>
       </c>
       <c r="C14" s="3">
-        <v>1462.3</v>
+        <v>1472.7</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1274,10 +1274,10 @@
         <v>16</v>
       </c>
       <c r="B15" s="3">
-        <v>1472.4</v>
+        <v>1489.9</v>
       </c>
       <c r="C15" s="3">
-        <v>1472.7</v>
+        <v>1490.9</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1285,10 +1285,10 @@
         <v>17</v>
       </c>
       <c r="B16" s="3">
-        <v>1489.9</v>
+        <v>1490.6</v>
       </c>
       <c r="C16" s="3">
-        <v>1490.9</v>
+        <v>1489.3</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1296,10 +1296,10 @@
         <v>18</v>
       </c>
       <c r="B17" s="3">
-        <v>1490.6</v>
+        <v>1491</v>
       </c>
       <c r="C17" s="3">
-        <v>1489.3</v>
+        <v>1493.4</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1307,10 +1307,10 @@
         <v>19</v>
       </c>
       <c r="B18" s="3">
-        <v>1491</v>
+        <v>1500.8</v>
       </c>
       <c r="C18" s="3">
-        <v>1493.4</v>
+        <v>1497.5</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1318,10 +1318,10 @@
         <v>20</v>
       </c>
       <c r="B19" s="3">
-        <v>1500.8</v>
+        <v>1500.3</v>
       </c>
       <c r="C19" s="3">
-        <v>1497.5</v>
+        <v>1492.9</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1329,10 +1329,10 @@
         <v>21</v>
       </c>
       <c r="B20" s="3">
-        <v>1500.3</v>
+        <v>1507.8</v>
       </c>
       <c r="C20" s="3">
-        <v>1492.9</v>
+        <v>1508.7</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1340,10 +1340,10 @@
         <v>22</v>
       </c>
       <c r="B21" s="3">
-        <v>1507.8</v>
+        <v>1506.8</v>
       </c>
       <c r="C21" s="3">
-        <v>1508.7</v>
+        <v>1496.7</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1351,10 +1351,10 @@
         <v>23</v>
       </c>
       <c r="B22" s="3">
-        <v>1506.8</v>
+        <v>1506.1</v>
       </c>
       <c r="C22" s="4">
-        <v>1508.7</v>
+        <v>1496.7</v>
       </c>
     </row>
   </sheetData>
